--- a/TestFiles/AdvanceAndAdjustment/[MLB]AdvanceStatement-AA.xlsx
+++ b/TestFiles/AdvanceAndAdjustment/[MLB]AdvanceStatement-AA.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -112,29 +112,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -150,7 +150,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -177,62 +184,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="17">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -527,166 +537,178 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.14785714285714" customWidth="1"/>
-    <col min="2" max="2" width="18.433571428571426" customWidth="1"/>
-    <col min="3" max="3" width="14.147857142857141" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.576428571428572" customWidth="1"/>
-    <col min="5" max="5" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.576428571428572" customWidth="1"/>
-    <col min="7" max="7" width="22.719285714285714" customWidth="1"/>
-    <col min="8" max="8" width="19.433571428571426" customWidth="1"/>
-    <col min="9" max="9" width="20.862142857142857" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.576428571428572" customWidth="1"/>
-    <col min="11" max="11" width="13.576428571428572" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.576428571428572" style="3" customWidth="1"/>
-    <col min="14" max="14" width="14.576428571428572" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.14785714285714" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.14785714285714" customWidth="1"/>
-    <col min="18" max="18" width="13.576428571428572" style="2" customWidth="1"/>
-    <col min="19" max="20" width="13.576428571428572" customWidth="1"/>
-    <col min="21" max="21" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="22" max="27" width="13.576428571428572" customWidth="1"/>
+    <col min="1" max="1" style="13" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="18.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="22.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="19.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="15" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="16" width="14.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="14" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="8">
         <v>600011</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>44197</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="10">
         <v>44197</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="9">
         <v>1</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="11">
         <v>78.9</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="11">
         <v>631.2</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="9">
         <v>0</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>25</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="10">
         <v>44197</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="U2" s="11">
+      <c r="U2" s="9">
         <v>789</v>
       </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
